--- a/artfynd/A 4757-2026 artfynd.xlsx
+++ b/artfynd/A 4757-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389018</v>
       </c>
       <c r="B2" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>131389031</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>131389030</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>131389017</v>
       </c>
       <c r="B5" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4757-2026 artfynd.xlsx
+++ b/artfynd/A 4757-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389018</v>
       </c>
       <c r="B2" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>131389031</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>131389030</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>131389017</v>
       </c>
       <c r="B5" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4757-2026 artfynd.xlsx
+++ b/artfynd/A 4757-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389018</v>
       </c>
       <c r="B2" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>131389031</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>131389030</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>131389017</v>
       </c>
       <c r="B5" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4757-2026 artfynd.xlsx
+++ b/artfynd/A 4757-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389018</v>
       </c>
       <c r="B2" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>131389031</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>131389030</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>131389017</v>
       </c>
       <c r="B5" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4757-2026 artfynd.xlsx
+++ b/artfynd/A 4757-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389018</v>
       </c>
       <c r="B2" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>131389031</v>
       </c>
       <c r="B3" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>131389030</v>
       </c>
       <c r="B4" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>131389017</v>
       </c>
       <c r="B5" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4757-2026 artfynd.xlsx
+++ b/artfynd/A 4757-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389018</v>
       </c>
       <c r="B2" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>131389031</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>131389030</v>
       </c>
       <c r="B4" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>131389017</v>
       </c>
       <c r="B5" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4757-2026 artfynd.xlsx
+++ b/artfynd/A 4757-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389018</v>
       </c>
       <c r="B2" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>131389031</v>
       </c>
       <c r="B3" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>131389030</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>131389017</v>
       </c>
       <c r="B5" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4757-2026 artfynd.xlsx
+++ b/artfynd/A 4757-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131389018</v>
       </c>
       <c r="B2" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>131389031</v>
       </c>
       <c r="B3" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>131389030</v>
       </c>
       <c r="B4" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>131389017</v>
       </c>
       <c r="B5" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 4757-2026 artfynd.xlsx
+++ b/artfynd/A 4757-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,30 +675,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131389018</v>
+        <v>131389030</v>
       </c>
       <c r="B2" t="n">
-        <v>91858</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458147</v>
+        <v>458247</v>
       </c>
       <c r="R2" t="n">
-        <v>7081476</v>
+        <v>7081366</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -742,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,11 +780,11 @@
         <v>131389031</v>
       </c>
       <c r="B3" t="n">
-        <v>79266</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -867,201 +876,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>131389030</v>
-      </c>
-      <c r="B4" t="n">
-        <v>79266</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Knulbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>458247</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7081366</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>131389017</v>
-      </c>
-      <c r="B5" t="n">
-        <v>91858</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Knulbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>458203</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7081595</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
